--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdcdfb72c56a1470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R570df14682444b99"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R570df14682444b99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26ef5807fa494006"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26ef5807fa494006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02665c545182430b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02665c545182430b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc515083d7104ac7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc515083d7104ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5ed996e5f564216"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5ed996e5f564216"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69d2cb9b86e447c8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69d2cb9b86e447c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd96550b29c814697"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd96550b29c814697"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf5e38799e1fa4ddd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf5e38799e1fa4ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Red74a03b8aba44bf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Red74a03b8aba44bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb7699181a8904c88"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb7699181a8904c88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3acd301bada74735"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3acd301bada74735"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf921473255da4833"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf921473255da4833"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd171939a744247fc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd171939a744247fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re155e5a04e8e42e6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re155e5a04e8e42e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73715b8d1d514825"/>
   </x:sheets>
 </x:workbook>
 </file>
